--- a/data/trans_bre/P0902-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P0902-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 5,7</t>
+          <t>-0,11; 6,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 12,82</t>
+          <t>4,81; 12,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,1; 15,17</t>
+          <t>6,56; 14,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 8,57</t>
+          <t>1,63; 8,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 92,93</t>
+          <t>-1,66; 97,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,07; 125,96</t>
+          <t>33,4; 124,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,86; 159,45</t>
+          <t>50,73; 156,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,96; 72,33</t>
+          <t>9,62; 69,28</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 8,11</t>
+          <t>2,52; 8,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 13,65</t>
+          <t>6,6; 13,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,95</t>
+          <t>4,56; 10,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 15,41</t>
+          <t>6,7; 16,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,96; 121,24</t>
+          <t>26,25; 118,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,17; 128,18</t>
+          <t>49,28; 128,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,98; 141,07</t>
+          <t>44,3; 140,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,65; 290,85</t>
+          <t>55,38; 302,82</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 11,73</t>
+          <t>4,22; 11,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,96</t>
+          <t>5,11; 12,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 12,19</t>
+          <t>5,38; 12,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 5,56</t>
+          <t>-8,47; 5,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,64; 164,55</t>
+          <t>38,05; 155,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,74; 166,63</t>
+          <t>47,58; 174,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,8; 205,23</t>
+          <t>61,26; 210,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 42,23</t>
+          <t>-53,33; 43,14</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 11,71</t>
+          <t>6,04; 12,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,99</t>
+          <t>4,84; 11,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 10,48</t>
+          <t>3,89; 10,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 10,56</t>
+          <t>2,96; 10,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,41; 168,88</t>
+          <t>66,52; 175,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,79; 111,94</t>
+          <t>38,03; 121,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,92; 130,11</t>
+          <t>35,81; 132,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,55; 97,06</t>
+          <t>23,7; 97,37</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,88</t>
+          <t>4,93; 8,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 10,76</t>
+          <t>7,06; 10,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,18</t>
+          <t>6,81; 10,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,04</t>
+          <t>3,09; 9,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,09; 104,62</t>
+          <t>56,61; 108,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,05; 107,88</t>
+          <t>59,77; 104,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,18; 119,32</t>
+          <t>66,81; 116,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,66; 91,91</t>
+          <t>26,11; 93,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P0902-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P0902-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 6,1</t>
+          <t>0,17; 5,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 12,64</t>
+          <t>4,91; 13,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 14,97</t>
+          <t>6,92; 15,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 8,51</t>
+          <t>1,41; 8,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 97,86</t>
+          <t>0,73; 97,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,4; 124,19</t>
+          <t>33,48; 127,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,73; 156,49</t>
+          <t>50,59; 156,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 69,28</t>
+          <t>8,96; 67,7</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,43</t>
+          <t>8,4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>115,77%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,25</t>
+          <t>2,57; 8,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 13,38</t>
+          <t>6,92; 13,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,7</t>
+          <t>4,54; 10,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 16,11</t>
+          <t>5,32; 11,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,25; 118,4</t>
+          <t>28,84; 121,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,28; 128,57</t>
+          <t>50,03; 129,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,3; 140,18</t>
+          <t>43,37; 135,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,38; 302,82</t>
+          <t>43,02; 114,49</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 11,53</t>
+          <t>4,42; 11,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 12,26</t>
+          <t>5,38; 12,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 12,33</t>
+          <t>5,91; 12,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 5,76</t>
+          <t>2,26; 9,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,05; 155,91</t>
+          <t>41,55; 149,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,58; 174,96</t>
+          <t>49,09; 177,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,26; 210,95</t>
+          <t>71,11; 219,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 43,14</t>
+          <t>14,6; 78,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,31</t>
+          <t>8,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>72,04%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 12,12</t>
+          <t>6,16; 12,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 11,55</t>
+          <t>4,94; 11,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 10,77</t>
+          <t>4,19; 10,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 10,6</t>
+          <t>5,98; 11,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,52; 175,49</t>
+          <t>65,58; 180,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,03; 121,2</t>
+          <t>38,86; 116,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,81; 132,91</t>
+          <t>35,2; 125,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,7; 97,37</t>
+          <t>44,89; 109,33</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>7,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,03</t>
+          <t>4,94; 8,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 10,66</t>
+          <t>7,22; 10,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,06</t>
+          <t>6,71; 10,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,1</t>
+          <t>5,68; 8,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,61; 108,33</t>
+          <t>55,91; 108,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,77; 104,4</t>
+          <t>61,6; 105,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,81; 116,04</t>
+          <t>67,2; 119,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,11; 93,42</t>
+          <t>42,25; 73,94</t>
         </is>
       </c>
     </row>
